--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96824</v>
+        <v>96829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96824</v>
+        <v>96829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136729376</v>
       </c>
       <c r="B5" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136729394</v>
       </c>
       <c r="B6" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136735371</v>
       </c>
       <c r="B7" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136735218</v>
       </c>
       <c r="B8" t="n">
-        <v>93048</v>
+        <v>93053</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136730636</v>
       </c>
       <c r="B9" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136730661</v>
       </c>
       <c r="B10" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>136729547</v>
       </c>
       <c r="B11" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>136730422</v>
       </c>
       <c r="B12" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>136735263</v>
       </c>
       <c r="B13" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136729233</v>
       </c>
       <c r="B14" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136748906</v>
       </c>
       <c r="B15" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136729196</v>
       </c>
       <c r="B16" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>136729252</v>
       </c>
       <c r="B29" t="n">
-        <v>58870</v>
+        <v>58872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>136730446</v>
       </c>
       <c r="B30" t="n">
-        <v>58870</v>
+        <v>58872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136729376</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136729394</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136735371</v>
       </c>
       <c r="B7" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136735218</v>
       </c>
       <c r="B8" t="n">
-        <v>93053</v>
+        <v>93055</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96831</v>
+        <v>96837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96831</v>
+        <v>96837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136729376</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136729394</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136735371</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136735218</v>
       </c>
       <c r="B8" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136730636</v>
       </c>
       <c r="B9" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136730661</v>
       </c>
       <c r="B10" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96837</v>
+        <v>96839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96837</v>
+        <v>96839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136729376</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136729394</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136735371</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136735218</v>
       </c>
       <c r="B8" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136730636</v>
       </c>
       <c r="B9" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136730661</v>
       </c>
       <c r="B10" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96839</v>
+        <v>96840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96839</v>
+        <v>96840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136729376</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136729394</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136735371</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136735218</v>
       </c>
       <c r="B8" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136730636</v>
       </c>
       <c r="B9" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136730661</v>
       </c>
       <c r="B10" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96840</v>
+        <v>96846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96840</v>
+        <v>96846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136729376</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136729394</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136735371</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136735218</v>
       </c>
       <c r="B8" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96846</v>
+        <v>96850</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96846</v>
+        <v>96850</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136729376</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136729394</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136735371</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136735218</v>
       </c>
       <c r="B8" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136730636</v>
       </c>
       <c r="B9" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136730661</v>
       </c>
       <c r="B10" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96850</v>
+        <v>96852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96850</v>
+        <v>96852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96852</v>
+        <v>96854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96852</v>
+        <v>96854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136729376</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136729394</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136735371</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136735218</v>
       </c>
       <c r="B8" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136730636</v>
       </c>
       <c r="B9" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136730661</v>
       </c>
       <c r="B10" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96854</v>
+        <v>96867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96854</v>
+        <v>96867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136729376</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136729394</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136735371</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136735218</v>
       </c>
       <c r="B8" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136730636</v>
       </c>
       <c r="B9" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136730661</v>
       </c>
       <c r="B10" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>136729547</v>
       </c>
       <c r="B11" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>136730422</v>
       </c>
       <c r="B12" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>136735263</v>
       </c>
       <c r="B13" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136729233</v>
       </c>
       <c r="B14" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136748906</v>
       </c>
       <c r="B15" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136729196</v>
       </c>
       <c r="B16" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>136729252</v>
       </c>
       <c r="B29" t="n">
-        <v>58872</v>
+        <v>58885</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>136730446</v>
       </c>
       <c r="B30" t="n">
-        <v>58872</v>
+        <v>58885</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96867</v>
+        <v>96869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96867</v>
+        <v>96869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136729376</v>
       </c>
       <c r="B5" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136729394</v>
       </c>
       <c r="B6" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136735371</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>136735218</v>
       </c>
       <c r="B8" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136730636</v>
       </c>
       <c r="B9" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136730661</v>
       </c>
       <c r="B10" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>136729547</v>
       </c>
       <c r="B11" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>136730422</v>
       </c>
       <c r="B12" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>136735263</v>
       </c>
       <c r="B13" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136729233</v>
       </c>
       <c r="B14" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>136748906</v>
       </c>
       <c r="B15" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>136729196</v>
       </c>
       <c r="B16" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>136729488</v>
       </c>
       <c r="B18" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>136729774</v>
       </c>
       <c r="B19" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>136729935</v>
       </c>
       <c r="B20" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>136730142</v>
       </c>
       <c r="B21" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136730179</v>
       </c>
       <c r="B22" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>136730836</v>
       </c>
       <c r="B23" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>136735176</v>
       </c>
       <c r="B24" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>136735272</v>
       </c>
       <c r="B25" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>136735278</v>
       </c>
       <c r="B26" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136729761</v>
       </c>
       <c r="B27" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>136730658</v>
       </c>
       <c r="B28" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>136729252</v>
       </c>
       <c r="B29" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>136730446</v>
       </c>
       <c r="B30" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -1146,11 +1146,7 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stormosseberget, Stormosseberget, Sm</t>
@@ -1679,11 +1675,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stormosseberget, Stormosseberget, Sm</t>
@@ -1796,11 +1788,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stormosseberget, Stormosseberget, Sm</t>
@@ -1915,11 +1903,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2027,11 +2011,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stormosseberget, Stormosseberget, Sm</t>
@@ -2146,11 +2126,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2254,11 +2230,7 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stormosseberget, Stormosseberget, Sm</t>
@@ -2374,11 +2346,7 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2610,11 +2578,7 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stormosseberget, Stormosseberget, Sm</t>
@@ -2842,11 +2806,7 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2954,11 +2914,7 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3188,11 +3144,7 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3300,11 +3252,7 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3412,11 +3360,7 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3524,11 +3468,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4513,11 +4453,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stormosseberget, Stormosseberget, Sm</t>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96869</v>
+        <v>96872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96869</v>
+        <v>96872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136729376</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136729394</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136735371</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136735218</v>
       </c>
       <c r="B8" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96872</v>
+        <v>96882</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96872</v>
+        <v>96882</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136729376</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136729394</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136735371</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136735218</v>
       </c>
       <c r="B8" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136730636</v>
       </c>
       <c r="B9" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>136730661</v>
       </c>
       <c r="B10" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>136729547</v>
       </c>
       <c r="B11" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136730422</v>
       </c>
       <c r="B12" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>136735263</v>
       </c>
       <c r="B13" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>136729233</v>
       </c>
       <c r="B14" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>136748906</v>
       </c>
       <c r="B15" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136729196</v>
       </c>
       <c r="B16" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>136730086</v>
       </c>
       <c r="B17" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136729488</v>
       </c>
       <c r="B18" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136729774</v>
       </c>
       <c r="B19" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>136729935</v>
       </c>
       <c r="B20" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>136730142</v>
       </c>
       <c r="B21" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>136730179</v>
       </c>
       <c r="B22" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>136730836</v>
       </c>
       <c r="B23" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>136735176</v>
       </c>
       <c r="B24" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>136735272</v>
       </c>
       <c r="B25" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>136735278</v>
       </c>
       <c r="B26" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>136729761</v>
       </c>
       <c r="B27" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>136730658</v>
       </c>
       <c r="B28" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>136729252</v>
       </c>
       <c r="B29" t="n">
-        <v>58887</v>
+        <v>58897</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>136730446</v>
       </c>
       <c r="B30" t="n">
-        <v>58887</v>
+        <v>58897</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 37653-2026 artfynd.xlsx
+++ b/artfynd/A 37653-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730666</v>
       </c>
       <c r="B2" t="n">
-        <v>96882</v>
+        <v>96883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136735365</v>
       </c>
       <c r="B3" t="n">
-        <v>96882</v>
+        <v>96883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136729119</v>
       </c>
       <c r="B4" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>136729376</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>136729394</v>
       </c>
       <c r="B6" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136735371</v>
       </c>
       <c r="B7" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136735218</v>
       </c>
       <c r="B8" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>136729097</v>
       </c>
       <c r="B31" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>136729520</v>
       </c>
       <c r="B32" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>136730863</v>
       </c>
       <c r="B33" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>136735289</v>
       </c>
       <c r="B34" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>136735360</v>
       </c>
       <c r="B35" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>136730541</v>
       </c>
       <c r="B36" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
